--- a/VerveStacks_KEN_grids_kan/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_KEN_grids_kan/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_KEN_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D767BAD3-F45D-4DCB-A722-350148C9835F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{30243BC6-16EA-4CF4-A8A8-498B44581730}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1103" yWindow="1103" windowWidth="21600" windowHeight="12682" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Veda" sheetId="1" r:id="rId1"/>
@@ -799,13 +799,13 @@
     <t>D</t>
   </si>
   <si>
-    <t>S03aH01,S02aH01,S01aH01,S04aH01</t>
+    <t>S01aH01,S04aH01,S02aH01,S03aH01</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S03aH03,S02aH02,S04aH02,S01aH03,S03aH02,S04aH03,S01aH02,S02aH03</t>
+    <t>S04aH02,S03aH03,S02aH03,S04aH03,S03aH02,S01aH02,S01aH03,S02aH02</t>
   </si>
   <si>
     <t>com_pkflx</t>
@@ -931,10 +931,10 @@
     <t>S07aH06</t>
   </si>
   <si>
-    <t>S04aH03,S07aH04,S05aH04,S06aH02,S06aH03,S02aH04,S02aH03,S07aH03,S01aH03,S05aH02,S05aH03,S06aH04,S04aH02,S02aH02,S01aH04,S07aH02,S03aH04,S03aH03,S01aH02,S04aH04,S03aH02</t>
+    <t>S03aH04,S04aH03,S07aH04,S02aH03,S07aH03,S05aH04,S06aH02,S06aH03,S02aH02,S06aH04,S02aH04,S03aH03,S03aH02,S01aH04,S07aH02,S01aH03,S05aH02,S05aH03,S04aH02,S01aH02,S04aH04</t>
   </si>
   <si>
-    <t>S02aH01,S05aH06,S01aH06,S07aH01,S02aH06,S03aH05,S05aH05,S01aH01,S04aH01,S04aH06,S04aH05,S06aH01,S02aH05,S07aH05,S03aH01,S05aH01,S07aH06,S06aH06,S01aH05,S03aH06,S06aH05</t>
+    <t>S05aH01,S07aH06,S02aH01,S05aH06,S01aH01,S04aH01,S04aH06,S01aH06,S07aH01,S03aH01,S04aH05,S06aH01,S02aH05,S02aH06,S03aH05,S05aH05,S06aH06,S07aH05,S01aH05,S03aH06,S06aH05</t>
   </si>
   <si>
     <t>AllS</t>
@@ -1000,10 +1000,10 @@
     <t>WaP</t>
   </si>
   <si>
-    <t>SaD,RaP,FaD,RaD,WaD,FaP,SaP,WaP</t>
+    <t>WaD,FaD,SaD,WaP,RaD,FaP,SaP,RaP</t>
   </si>
   <si>
-    <t>FaP,SaP,WaP,FaN,RaP,SaN,WaN,RaN</t>
+    <t>FaN,RaP,FaP,SaP,RaN,SaN,WaN,WaP</t>
   </si>
 </sst>
 </file>
@@ -24707,7 +24707,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1096109F-AD13-487D-A204-BF70585CDE96}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF66E133-C7B8-456C-B256-2F1D3CC6932C}">
   <dimension ref="A9:AN346"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -26014,7 +26014,7 @@
         <v>158</v>
       </c>
       <c r="AM25">
-        <v>0.3714142857142857</v>
+        <v>0.37141428571428575</v>
       </c>
       <c r="AN25" t="s">
         <v>245</v>
@@ -26486,7 +26486,7 @@
         <v>158</v>
       </c>
       <c r="AM33">
-        <v>0.50291428571428565</v>
+        <v>0.50291428571428576</v>
       </c>
       <c r="AN33" t="s">
         <v>245</v>
@@ -28495,7 +28495,7 @@
         <v>158</v>
       </c>
       <c r="AM73">
-        <v>0.45615714285714287</v>
+        <v>0.45615714285714282</v>
       </c>
       <c r="AN73" t="s">
         <v>245</v>
@@ -30095,7 +30095,7 @@
         <v>158</v>
       </c>
       <c r="AM105">
-        <v>0.42919999999999997</v>
+        <v>0.42920000000000008</v>
       </c>
       <c r="AN105" t="s">
         <v>245</v>
@@ -30295,7 +30295,7 @@
         <v>158</v>
       </c>
       <c r="AM109">
-        <v>0.38769999999999999</v>
+        <v>0.38770000000000004</v>
       </c>
       <c r="AN109" t="s">
         <v>245</v>
@@ -30895,7 +30895,7 @@
         <v>158</v>
       </c>
       <c r="AM121">
-        <v>0.36812857142857147</v>
+        <v>0.36812857142857142</v>
       </c>
       <c r="AN121" t="s">
         <v>245</v>
@@ -36205,7 +36205,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF8BC73D-6DFF-4186-8A47-C622EE3CF403}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC42FDFC-2847-4F1D-9D5F-52DE33F96225}">
   <dimension ref="A9:AN1186"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -37282,7 +37282,7 @@
         <v>160</v>
       </c>
       <c r="AM21">
-        <v>0.49418604651162801</v>
+        <v>0.4941860465116279</v>
       </c>
       <c r="AN21" t="s">
         <v>245</v>
@@ -37842,7 +37842,7 @@
         <v>160</v>
       </c>
       <c r="AM28">
-        <v>0.40520546803367513</v>
+        <v>0.40520546803367508</v>
       </c>
       <c r="AN28" t="s">
         <v>245</v>
@@ -44190,7 +44190,7 @@
         <v>160</v>
       </c>
       <c r="AM133">
-        <v>0.44205999999999995</v>
+        <v>0.44206000000000001</v>
       </c>
       <c r="AN133" t="s">
         <v>245</v>
@@ -44540,7 +44540,7 @@
         <v>160</v>
       </c>
       <c r="AM140">
-        <v>0.43318000000000001</v>
+        <v>0.43317999999999995</v>
       </c>
       <c r="AN140" t="s">
         <v>245</v>
@@ -44890,7 +44890,7 @@
         <v>160</v>
       </c>
       <c r="AM147">
-        <v>0.45234000000000008</v>
+        <v>0.45233999999999996</v>
       </c>
       <c r="AN147" t="s">
         <v>245</v>
@@ -45240,7 +45240,7 @@
         <v>160</v>
       </c>
       <c r="AM154">
-        <v>0.43946000000000007</v>
+        <v>0.43945999999999996</v>
       </c>
       <c r="AN154" t="s">
         <v>245</v>
@@ -46290,7 +46290,7 @@
         <v>160</v>
       </c>
       <c r="AM175">
-        <v>0.41842000000000007</v>
+        <v>0.41841999999999996</v>
       </c>
       <c r="AN175" t="s">
         <v>245</v>
@@ -46640,7 +46640,7 @@
         <v>160</v>
       </c>
       <c r="AM182">
-        <v>0.38904</v>
+        <v>0.38903999999999994</v>
       </c>
       <c r="AN182" t="s">
         <v>245</v>
@@ -73584,7 +73584,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80E504CE-095A-44A8-89BF-39B5C43FFC51}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5AE5E61-3183-4257-9D35-5FABAABF1E24}">
   <dimension ref="A9:AN39"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -73813,7 +73813,7 @@
         <v>285</v>
       </c>
       <c r="AM11">
-        <v>0.56918725962761829</v>
+        <v>0.56918725962761818</v>
       </c>
       <c r="AN11" t="s">
         <v>245</v>
@@ -74172,7 +74172,7 @@
         <v>285</v>
       </c>
       <c r="AM18">
-        <v>0.51738333333333342</v>
+        <v>0.51738333333333331</v>
       </c>
       <c r="AN18" t="s">
         <v>245</v>
@@ -74272,7 +74272,7 @@
         <v>285</v>
       </c>
       <c r="AM20">
-        <v>0.44666666666666671</v>
+        <v>0.4466666666666666</v>
       </c>
       <c r="AN20" t="s">
         <v>245</v>
@@ -74348,7 +74348,7 @@
         <v>285</v>
       </c>
       <c r="AM22">
-        <v>0.44695833333333335</v>
+        <v>0.44695833333333329</v>
       </c>
       <c r="AN22" t="s">
         <v>245</v>
@@ -74424,7 +74424,7 @@
         <v>285</v>
       </c>
       <c r="AM24">
-        <v>0.44499166666666667</v>
+        <v>0.44499166666666673</v>
       </c>
       <c r="AN24" t="s">
         <v>245</v>
@@ -74462,7 +74462,7 @@
         <v>285</v>
       </c>
       <c r="AM25">
-        <v>0.45474166666666677</v>
+        <v>0.45474166666666666</v>
       </c>
       <c r="AN25" t="s">
         <v>245</v>
@@ -74576,7 +74576,7 @@
         <v>285</v>
       </c>
       <c r="AM28">
-        <v>0.44241666666666668</v>
+        <v>0.44241666666666674</v>
       </c>
       <c r="AN28" t="s">
         <v>245</v>
@@ -74652,7 +74652,7 @@
         <v>285</v>
       </c>
       <c r="AM30">
-        <v>0.44701666666666662</v>
+        <v>0.44701666666666667</v>
       </c>
       <c r="AN30" t="s">
         <v>245</v>
@@ -74792,7 +74792,7 @@
         <v>285</v>
       </c>
       <c r="AM34">
-        <v>0.43429166666666669</v>
+        <v>0.43429166666666674</v>
       </c>
       <c r="AN34" t="s">
         <v>245</v>
@@ -74818,7 +74818,7 @@
         <v>285</v>
       </c>
       <c r="AM35">
-        <v>0.38326666666666664</v>
+        <v>0.38326666666666659</v>
       </c>
       <c r="AN35" t="s">
         <v>245</v>
@@ -74844,7 +74844,7 @@
         <v>285</v>
       </c>
       <c r="AM36">
-        <v>0.38044166666666673</v>
+        <v>0.38044166666666662</v>
       </c>
       <c r="AN36" t="s">
         <v>245</v>
@@ -74910,7 +74910,7 @@
         <v>285</v>
       </c>
       <c r="AM39">
-        <v>0.37856666666666666</v>
+        <v>0.37856666666666672</v>
       </c>
       <c r="AN39" t="s">
         <v>245</v>
@@ -74922,7 +74922,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{705DFDCE-7471-49E8-AE20-E7E3A7CC4091}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D06DC863-1AEA-4F27-9667-3B67679A50E7}">
   <dimension ref="A9:AN346"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -75492,7 +75492,7 @@
         <v>288</v>
       </c>
       <c r="AM15">
-        <v>0.45757967269595179</v>
+        <v>0.45757967269595173</v>
       </c>
       <c r="AN15" t="s">
         <v>245</v>
@@ -75892,7 +75892,7 @@
         <v>290</v>
       </c>
       <c r="AM20">
-        <v>0.39471673473924035</v>
+        <v>0.3947167347392404</v>
       </c>
       <c r="AN20" t="s">
         <v>245</v>
@@ -76229,7 +76229,7 @@
         <v>291</v>
       </c>
       <c r="AM25">
-        <v>0.37539999999999996</v>
+        <v>0.37540000000000001</v>
       </c>
       <c r="AN25" t="s">
         <v>245</v>
@@ -76642,7 +76642,7 @@
         <v>290</v>
       </c>
       <c r="AM32">
-        <v>0.4781333333333333</v>
+        <v>0.47813333333333335</v>
       </c>
       <c r="AN32" t="s">
         <v>245</v>
@@ -77310,7 +77310,7 @@
         <v>291</v>
       </c>
       <c r="AM45">
-        <v>0.52269999999999994</v>
+        <v>0.52270000000000005</v>
       </c>
       <c r="AN45" t="s">
         <v>245</v>
@@ -77410,7 +77410,7 @@
         <v>288</v>
       </c>
       <c r="AM47">
-        <v>0.44223333333333331</v>
+        <v>0.44223333333333342</v>
       </c>
       <c r="AN47" t="s">
         <v>245</v>
@@ -77810,7 +77810,7 @@
         <v>288</v>
       </c>
       <c r="AM55">
-        <v>0.47316666666666668</v>
+        <v>0.47316666666666674</v>
       </c>
       <c r="AN55" t="s">
         <v>245</v>
@@ -78060,7 +78060,7 @@
         <v>290</v>
       </c>
       <c r="AM60">
-        <v>0.40983333333333333</v>
+        <v>0.40983333333333327</v>
       </c>
       <c r="AN60" t="s">
         <v>245</v>
@@ -78660,7 +78660,7 @@
         <v>290</v>
       </c>
       <c r="AM72">
-        <v>0.43156666666666671</v>
+        <v>0.43156666666666665</v>
       </c>
       <c r="AN72" t="s">
         <v>245</v>
@@ -79110,7 +79110,7 @@
         <v>291</v>
       </c>
       <c r="AM81">
-        <v>0.43593333333333328</v>
+        <v>0.43593333333333334</v>
       </c>
       <c r="AN81" t="s">
         <v>245</v>
@@ -79210,7 +79210,7 @@
         <v>288</v>
       </c>
       <c r="AM83">
-        <v>0.47026666666666667</v>
+        <v>0.47026666666666661</v>
       </c>
       <c r="AN83" t="s">
         <v>245</v>
@@ -79810,7 +79810,7 @@
         <v>288</v>
       </c>
       <c r="AM95">
-        <v>0.44166666666666665</v>
+        <v>0.44166666666666671</v>
       </c>
       <c r="AN95" t="s">
         <v>245</v>
@@ -80010,7 +80010,7 @@
         <v>288</v>
       </c>
       <c r="AM99">
-        <v>0.47016666666666662</v>
+        <v>0.47016666666666668</v>
       </c>
       <c r="AN99" t="s">
         <v>245</v>
@@ -80260,7 +80260,7 @@
         <v>290</v>
       </c>
       <c r="AM104">
-        <v>0.42699999999999999</v>
+        <v>0.42700000000000005</v>
       </c>
       <c r="AN104" t="s">
         <v>245</v>
@@ -81010,7 +81010,7 @@
         <v>288</v>
       </c>
       <c r="AM119">
-        <v>0.34783333333333327</v>
+        <v>0.34783333333333338</v>
       </c>
       <c r="AN119" t="s">
         <v>245</v>
@@ -81060,7 +81060,7 @@
         <v>290</v>
       </c>
       <c r="AM120">
-        <v>0.34770000000000006</v>
+        <v>0.34769999999999995</v>
       </c>
       <c r="AN120" t="s">
         <v>245</v>

--- a/VerveStacks_KEN_grids_kan/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_KEN_grids_kan/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_KEN_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{30243BC6-16EA-4CF4-A8A8-498B44581730}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A64267D2-B2E5-4BB1-B270-84ED238DBC82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -805,7 +805,7 @@
     <t>N</t>
   </si>
   <si>
-    <t>S04aH02,S03aH03,S02aH03,S04aH03,S03aH02,S01aH02,S01aH03,S02aH02</t>
+    <t>S04aH02,S03aH02,S02aH03,S01aH02,S04aH03,S01aH03,S03aH03,S02aH02</t>
   </si>
   <si>
     <t>com_pkflx</t>
@@ -931,10 +931,10 @@
     <t>S07aH06</t>
   </si>
   <si>
-    <t>S03aH04,S04aH03,S07aH04,S02aH03,S07aH03,S05aH04,S06aH02,S06aH03,S02aH02,S06aH04,S02aH04,S03aH03,S03aH02,S01aH04,S07aH02,S01aH03,S05aH02,S05aH03,S04aH02,S01aH02,S04aH04</t>
+    <t>S03aH04,S03aH03,S05aH04,S06aH02,S06aH03,S02aH03,S07aH03,S06aH04,S04aH02,S02aH02,S02aH04,S01aH03,S05aH02,S05aH03,S01aH02,S04aH04,S04aH03,S07aH04,S01aH04,S07aH02,S03aH02</t>
   </si>
   <si>
-    <t>S05aH01,S07aH06,S02aH01,S05aH06,S01aH01,S04aH01,S04aH06,S01aH06,S07aH01,S03aH01,S04aH05,S06aH01,S02aH05,S02aH06,S03aH05,S05aH05,S06aH06,S07aH05,S01aH05,S03aH06,S06aH05</t>
+    <t>S05aH01,S07aH06,S06aH06,S01aH06,S07aH01,S04aH05,S06aH01,S01aH01,S04aH01,S04aH06,S02aH05,S07aH05,S03aH01,S02aH06,S03aH05,S05aH05,S01aH05,S03aH06,S06aH05,S02aH01,S05aH06</t>
   </si>
   <si>
     <t>AllS</t>
@@ -1000,10 +1000,10 @@
     <t>WaP</t>
   </si>
   <si>
-    <t>WaD,FaD,SaD,WaP,RaD,FaP,SaP,RaP</t>
+    <t>FaP,SaP,SaD,FaD,WaD,WaP,RaP,RaD</t>
   </si>
   <si>
-    <t>FaN,RaP,FaP,SaP,RaN,SaN,WaN,WaP</t>
+    <t>WaP,FaP,SaP,SaN,WaN,RaP,RaN,FaN</t>
   </si>
 </sst>
 </file>
@@ -24707,7 +24707,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF66E133-C7B8-456C-B256-2F1D3CC6932C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93A2C272-E26D-4F72-AC83-FDB2597E96EF}">
   <dimension ref="A9:AN346"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -25114,7 +25114,7 @@
         <v>158</v>
       </c>
       <c r="AM13">
-        <v>0.5496069395500135</v>
+        <v>0.54960693955001361</v>
       </c>
       <c r="AN13" t="s">
         <v>245</v>
@@ -26250,7 +26250,7 @@
         <v>158</v>
       </c>
       <c r="AM29">
-        <v>0.44557142857142856</v>
+        <v>0.44557142857142862</v>
       </c>
       <c r="AN29" t="s">
         <v>245</v>
@@ -28095,7 +28095,7 @@
         <v>158</v>
       </c>
       <c r="AM65">
-        <v>0.43875714285714285</v>
+        <v>0.43875714285714279</v>
       </c>
       <c r="AN65" t="s">
         <v>245</v>
@@ -28295,7 +28295,7 @@
         <v>158</v>
       </c>
       <c r="AM69">
-        <v>0.4516857142857143</v>
+        <v>0.45168571428571436</v>
       </c>
       <c r="AN69" t="s">
         <v>245</v>
@@ -28895,7 +28895,7 @@
         <v>158</v>
       </c>
       <c r="AM81">
-        <v>0.43668571428571429</v>
+        <v>0.43668571428571434</v>
       </c>
       <c r="AN81" t="s">
         <v>245</v>
@@ -30295,7 +30295,7 @@
         <v>158</v>
       </c>
       <c r="AM109">
-        <v>0.38770000000000004</v>
+        <v>0.38769999999999999</v>
       </c>
       <c r="AN109" t="s">
         <v>245</v>
@@ -30495,7 +30495,7 @@
         <v>158</v>
       </c>
       <c r="AM113">
-        <v>0.38677142857142854</v>
+        <v>0.3867714285714286</v>
       </c>
       <c r="AN113" t="s">
         <v>245</v>
@@ -31095,7 +31095,7 @@
         <v>158</v>
       </c>
       <c r="AM125">
-        <v>0.3771714285714286</v>
+        <v>0.37717142857142855</v>
       </c>
       <c r="AN125" t="s">
         <v>245</v>
@@ -36205,7 +36205,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC42FDFC-2847-4F1D-9D5F-52DE33F96225}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18915CF8-06AC-4AD9-AE3F-B725A3EF28AC}">
   <dimension ref="A9:AN1186"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -39522,7 +39522,7 @@
         <v>160</v>
       </c>
       <c r="AM49">
-        <v>0.49715999999999994</v>
+        <v>0.49716000000000005</v>
       </c>
       <c r="AN49" t="s">
         <v>245</v>
@@ -39998,7 +39998,7 @@
         <v>160</v>
       </c>
       <c r="AM56">
-        <v>0.52046000000000003</v>
+        <v>0.52045999999999992</v>
       </c>
       <c r="AN56" t="s">
         <v>245</v>
@@ -45940,7 +45940,7 @@
         <v>160</v>
       </c>
       <c r="AM168">
-        <v>0.44874000000000003</v>
+        <v>0.44873999999999992</v>
       </c>
       <c r="AN168" t="s">
         <v>245</v>
@@ -46290,7 +46290,7 @@
         <v>160</v>
       </c>
       <c r="AM175">
-        <v>0.41841999999999996</v>
+        <v>0.41842000000000007</v>
       </c>
       <c r="AN175" t="s">
         <v>245</v>
@@ -46990,7 +46990,7 @@
         <v>160</v>
       </c>
       <c r="AM189">
-        <v>0.39017999999999997</v>
+        <v>0.39018000000000003</v>
       </c>
       <c r="AN189" t="s">
         <v>245</v>
@@ -47340,7 +47340,7 @@
         <v>160</v>
       </c>
       <c r="AM196">
-        <v>0.35652</v>
+        <v>0.35651999999999995</v>
       </c>
       <c r="AN196" t="s">
         <v>245</v>
@@ -73584,7 +73584,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5AE5E61-3183-4257-9D35-5FABAABF1E24}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8C03F53-C24E-4BF5-B296-884D93D0C75B}">
   <dimension ref="A9:AN39"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -73813,7 +73813,7 @@
         <v>285</v>
       </c>
       <c r="AM11">
-        <v>0.56918725962761818</v>
+        <v>0.56918725962761829</v>
       </c>
       <c r="AN11" t="s">
         <v>245</v>
@@ -73872,7 +73872,7 @@
         <v>285</v>
       </c>
       <c r="AM12">
-        <v>0.48831652357533822</v>
+        <v>0.48831652357533833</v>
       </c>
       <c r="AN12" t="s">
         <v>245</v>
@@ -73922,7 +73922,7 @@
         <v>285</v>
       </c>
       <c r="AM13">
-        <v>0.40084425868371848</v>
+        <v>0.40084425868371859</v>
       </c>
       <c r="AN13" t="s">
         <v>245</v>
@@ -73972,7 +73972,7 @@
         <v>285</v>
       </c>
       <c r="AM14">
-        <v>0.3788583333333333</v>
+        <v>0.37885833333333335</v>
       </c>
       <c r="AN14" t="s">
         <v>245</v>
@@ -74022,7 +74022,7 @@
         <v>285</v>
       </c>
       <c r="AM15">
-        <v>0.45091666666666663</v>
+        <v>0.4509166666666668</v>
       </c>
       <c r="AN15" t="s">
         <v>245</v>
@@ -74172,7 +74172,7 @@
         <v>285</v>
       </c>
       <c r="AM18">
-        <v>0.51738333333333331</v>
+        <v>0.5173833333333332</v>
       </c>
       <c r="AN18" t="s">
         <v>245</v>
@@ -74348,7 +74348,7 @@
         <v>285</v>
       </c>
       <c r="AM22">
-        <v>0.44695833333333329</v>
+        <v>0.4469583333333334</v>
       </c>
       <c r="AN22" t="s">
         <v>245</v>
@@ -74500,7 +74500,7 @@
         <v>285</v>
       </c>
       <c r="AM26">
-        <v>0.45130833333333337</v>
+        <v>0.45130833333333326</v>
       </c>
       <c r="AN26" t="s">
         <v>245</v>
@@ -74614,7 +74614,7 @@
         <v>285</v>
       </c>
       <c r="AM29">
-        <v>0.44884999999999997</v>
+        <v>0.44885000000000003</v>
       </c>
       <c r="AN29" t="s">
         <v>245</v>
@@ -74652,7 +74652,7 @@
         <v>285</v>
       </c>
       <c r="AM30">
-        <v>0.44701666666666667</v>
+        <v>0.44701666666666662</v>
       </c>
       <c r="AN30" t="s">
         <v>245</v>
@@ -74690,7 +74690,7 @@
         <v>285</v>
       </c>
       <c r="AM31">
-        <v>0.43934166666666669</v>
+        <v>0.43934166666666657</v>
       </c>
       <c r="AN31" t="s">
         <v>245</v>
@@ -74728,7 +74728,7 @@
         <v>285</v>
       </c>
       <c r="AM32">
-        <v>0.44870833333333332</v>
+        <v>0.44870833333333343</v>
       </c>
       <c r="AN32" t="s">
         <v>245</v>
@@ -74766,7 +74766,7 @@
         <v>285</v>
       </c>
       <c r="AM33">
-        <v>0.45370833333333332</v>
+        <v>0.45370833333333321</v>
       </c>
       <c r="AN33" t="s">
         <v>245</v>
@@ -74818,7 +74818,7 @@
         <v>285</v>
       </c>
       <c r="AM35">
-        <v>0.38326666666666659</v>
+        <v>0.38326666666666664</v>
       </c>
       <c r="AN35" t="s">
         <v>245</v>
@@ -74870,7 +74870,7 @@
         <v>285</v>
       </c>
       <c r="AM37">
-        <v>0.37212500000000004</v>
+        <v>0.37212499999999998</v>
       </c>
       <c r="AN37" t="s">
         <v>245</v>
@@ -74922,7 +74922,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D06DC863-1AEA-4F27-9667-3B67679A50E7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C20300F0-29DA-436E-98B9-33E58DAC32F2}">
   <dimension ref="A9:AN346"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -75492,7 +75492,7 @@
         <v>288</v>
       </c>
       <c r="AM15">
-        <v>0.45757967269595173</v>
+        <v>0.45757967269595179</v>
       </c>
       <c r="AN15" t="s">
         <v>245</v>
@@ -77310,7 +77310,7 @@
         <v>291</v>
       </c>
       <c r="AM45">
-        <v>0.52270000000000005</v>
+        <v>0.52269999999999994</v>
       </c>
       <c r="AN45" t="s">
         <v>245</v>
@@ -77410,7 +77410,7 @@
         <v>288</v>
       </c>
       <c r="AM47">
-        <v>0.44223333333333342</v>
+        <v>0.44223333333333331</v>
       </c>
       <c r="AN47" t="s">
         <v>245</v>
@@ -77810,7 +77810,7 @@
         <v>288</v>
       </c>
       <c r="AM55">
-        <v>0.47316666666666674</v>
+        <v>0.47316666666666668</v>
       </c>
       <c r="AN55" t="s">
         <v>245</v>
@@ -79110,7 +79110,7 @@
         <v>291</v>
       </c>
       <c r="AM81">
-        <v>0.43593333333333334</v>
+        <v>0.43593333333333328</v>
       </c>
       <c r="AN81" t="s">
         <v>245</v>
@@ -79210,7 +79210,7 @@
         <v>288</v>
       </c>
       <c r="AM83">
-        <v>0.47026666666666661</v>
+        <v>0.47026666666666667</v>
       </c>
       <c r="AN83" t="s">
         <v>245</v>
@@ -79310,7 +79310,7 @@
         <v>291</v>
       </c>
       <c r="AM85">
-        <v>0.43659999999999993</v>
+        <v>0.43660000000000004</v>
       </c>
       <c r="AN85" t="s">
         <v>245</v>
@@ -79710,7 +79710,7 @@
         <v>291</v>
       </c>
       <c r="AM93">
-        <v>0.4592</v>
+        <v>0.45920000000000005</v>
       </c>
       <c r="AN93" t="s">
         <v>245</v>
@@ -79810,7 +79810,7 @@
         <v>288</v>
       </c>
       <c r="AM95">
-        <v>0.44166666666666671</v>
+        <v>0.44166666666666665</v>
       </c>
       <c r="AN95" t="s">
         <v>245</v>
@@ -80010,7 +80010,7 @@
         <v>288</v>
       </c>
       <c r="AM99">
-        <v>0.47016666666666668</v>
+        <v>0.47016666666666662</v>
       </c>
       <c r="AN99" t="s">
         <v>245</v>
@@ -81010,7 +81010,7 @@
         <v>288</v>
       </c>
       <c r="AM119">
-        <v>0.34783333333333338</v>
+        <v>0.34783333333333327</v>
       </c>
       <c r="AN119" t="s">
         <v>245</v>

--- a/VerveStacks_KEN_grids_kan/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_KEN_grids_kan/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_KEN_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A64267D2-B2E5-4BB1-B270-84ED238DBC82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C9FBF56C-C9E6-4B06-B2B5-7839EF9F111B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -799,13 +799,13 @@
     <t>D</t>
   </si>
   <si>
-    <t>S01aH01,S04aH01,S02aH01,S03aH01</t>
+    <t>S02aH01,S03aH01,S01aH01,S04aH01</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S04aH02,S03aH02,S02aH03,S01aH02,S04aH03,S01aH03,S03aH03,S02aH02</t>
+    <t>S04aH03,S02aH02,S01aH03,S01aH02,S02aH03,S04aH02,S03aH03,S03aH02</t>
   </si>
   <si>
     <t>com_pkflx</t>
@@ -931,10 +931,10 @@
     <t>S07aH06</t>
   </si>
   <si>
-    <t>S03aH04,S03aH03,S05aH04,S06aH02,S06aH03,S02aH03,S07aH03,S06aH04,S04aH02,S02aH02,S02aH04,S01aH03,S05aH02,S05aH03,S01aH02,S04aH04,S04aH03,S07aH04,S01aH04,S07aH02,S03aH02</t>
+    <t>S06aH04,S02aH04,S01aH03,S05aH02,S05aH03,S03aH02,S03aH04,S02aH03,S07aH03,S01aH02,S04aH04,S02aH02,S01aH04,S07aH02,S04aH03,S07aH04,S04aH02,S05aH04,S06aH02,S06aH03,S03aH03</t>
   </si>
   <si>
-    <t>S05aH01,S07aH06,S06aH06,S01aH06,S07aH01,S04aH05,S06aH01,S01aH01,S04aH01,S04aH06,S02aH05,S07aH05,S03aH01,S02aH06,S03aH05,S05aH05,S01aH05,S03aH06,S06aH05,S02aH01,S05aH06</t>
+    <t>S02aH05,S02aH06,S03aH05,S05aH05,S04aH05,S06aH01,S05aH01,S07aH06,S01aH01,S04aH01,S04aH06,S01aH05,S03aH06,S06aH05,S03aH01,S02aH01,S05aH06,S07aH05,S01aH06,S07aH01,S06aH06</t>
   </si>
   <si>
     <t>AllS</t>
@@ -1000,10 +1000,10 @@
     <t>WaP</t>
   </si>
   <si>
-    <t>FaP,SaP,SaD,FaD,WaD,WaP,RaP,RaD</t>
+    <t>FaD,RaP,SaD,FaP,SaP,WaD,RaD,WaP</t>
   </si>
   <si>
-    <t>WaP,FaP,SaP,SaN,WaN,RaP,RaN,FaN</t>
+    <t>RaP,WaP,FaP,SaP,SaN,WaN,FaN,RaN</t>
   </si>
 </sst>
 </file>
@@ -24707,7 +24707,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93A2C272-E26D-4F72-AC83-FDB2597E96EF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA1A6B3F-42DD-4477-8E1B-63F19CB41BDC}">
   <dimension ref="A9:AN346"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -25114,7 +25114,7 @@
         <v>158</v>
       </c>
       <c r="AM13">
-        <v>0.54960693955001361</v>
+        <v>0.5496069395500135</v>
       </c>
       <c r="AN13" t="s">
         <v>245</v>
@@ -26014,7 +26014,7 @@
         <v>158</v>
       </c>
       <c r="AM25">
-        <v>0.37141428571428575</v>
+        <v>0.3714142857142857</v>
       </c>
       <c r="AN25" t="s">
         <v>245</v>
@@ -27895,7 +27895,7 @@
         <v>158</v>
       </c>
       <c r="AM61">
-        <v>0.43405714285714286</v>
+        <v>0.43405714285714281</v>
       </c>
       <c r="AN61" t="s">
         <v>245</v>
@@ -28095,7 +28095,7 @@
         <v>158</v>
       </c>
       <c r="AM65">
-        <v>0.43875714285714279</v>
+        <v>0.43875714285714285</v>
       </c>
       <c r="AN65" t="s">
         <v>245</v>
@@ -28295,7 +28295,7 @@
         <v>158</v>
       </c>
       <c r="AM69">
-        <v>0.45168571428571436</v>
+        <v>0.4516857142857143</v>
       </c>
       <c r="AN69" t="s">
         <v>245</v>
@@ -28495,7 +28495,7 @@
         <v>158</v>
       </c>
       <c r="AM73">
-        <v>0.45615714285714282</v>
+        <v>0.45615714285714287</v>
       </c>
       <c r="AN73" t="s">
         <v>245</v>
@@ -28895,7 +28895,7 @@
         <v>158</v>
       </c>
       <c r="AM81">
-        <v>0.43668571428571434</v>
+        <v>0.43668571428571429</v>
       </c>
       <c r="AN81" t="s">
         <v>245</v>
@@ -29495,7 +29495,7 @@
         <v>158</v>
       </c>
       <c r="AM93">
-        <v>0.42887142857142857</v>
+        <v>0.42887142857142863</v>
       </c>
       <c r="AN93" t="s">
         <v>245</v>
@@ -30095,7 +30095,7 @@
         <v>158</v>
       </c>
       <c r="AM105">
-        <v>0.42920000000000008</v>
+        <v>0.42919999999999991</v>
       </c>
       <c r="AN105" t="s">
         <v>245</v>
@@ -30495,7 +30495,7 @@
         <v>158</v>
       </c>
       <c r="AM113">
-        <v>0.3867714285714286</v>
+        <v>0.38677142857142854</v>
       </c>
       <c r="AN113" t="s">
         <v>245</v>
@@ -30895,7 +30895,7 @@
         <v>158</v>
       </c>
       <c r="AM121">
-        <v>0.36812857142857142</v>
+        <v>0.36812857142857147</v>
       </c>
       <c r="AN121" t="s">
         <v>245</v>
@@ -31095,7 +31095,7 @@
         <v>158</v>
       </c>
       <c r="AM125">
-        <v>0.37717142857142855</v>
+        <v>0.3771714285714286</v>
       </c>
       <c r="AN125" t="s">
         <v>245</v>
@@ -36205,7 +36205,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18915CF8-06AC-4AD9-AE3F-B725A3EF28AC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{880C3CAD-F8C4-4449-803F-96D991B523B2}">
   <dimension ref="A9:AN1186"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -41650,7 +41650,7 @@
         <v>160</v>
       </c>
       <c r="AM84">
-        <v>0.44190000000000007</v>
+        <v>0.44189999999999996</v>
       </c>
       <c r="AN84" t="s">
         <v>245</v>
@@ -44190,7 +44190,7 @@
         <v>160</v>
       </c>
       <c r="AM133">
-        <v>0.44206000000000001</v>
+        <v>0.44205999999999995</v>
       </c>
       <c r="AN133" t="s">
         <v>245</v>
@@ -44540,7 +44540,7 @@
         <v>160</v>
       </c>
       <c r="AM140">
-        <v>0.43317999999999995</v>
+        <v>0.43318000000000001</v>
       </c>
       <c r="AN140" t="s">
         <v>245</v>
@@ -44890,7 +44890,7 @@
         <v>160</v>
       </c>
       <c r="AM147">
-        <v>0.45233999999999996</v>
+        <v>0.45234000000000008</v>
       </c>
       <c r="AN147" t="s">
         <v>245</v>
@@ -45940,7 +45940,7 @@
         <v>160</v>
       </c>
       <c r="AM168">
-        <v>0.44873999999999992</v>
+        <v>0.44874000000000003</v>
       </c>
       <c r="AN168" t="s">
         <v>245</v>
@@ -46640,7 +46640,7 @@
         <v>160</v>
       </c>
       <c r="AM182">
-        <v>0.38903999999999994</v>
+        <v>0.38904</v>
       </c>
       <c r="AN182" t="s">
         <v>245</v>
@@ -46990,7 +46990,7 @@
         <v>160</v>
       </c>
       <c r="AM189">
-        <v>0.39018000000000003</v>
+        <v>0.39017999999999997</v>
       </c>
       <c r="AN189" t="s">
         <v>245</v>
@@ -47340,7 +47340,7 @@
         <v>160</v>
       </c>
       <c r="AM196">
-        <v>0.35651999999999995</v>
+        <v>0.35652</v>
       </c>
       <c r="AN196" t="s">
         <v>245</v>
@@ -73584,7 +73584,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8C03F53-C24E-4BF5-B296-884D93D0C75B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26DDBE97-F47F-48E6-970C-B4CDD6D69964}">
   <dimension ref="A9:AN39"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -73922,7 +73922,7 @@
         <v>285</v>
       </c>
       <c r="AM13">
-        <v>0.40084425868371859</v>
+        <v>0.40084425868371848</v>
       </c>
       <c r="AN13" t="s">
         <v>245</v>
@@ -74022,7 +74022,7 @@
         <v>285</v>
       </c>
       <c r="AM15">
-        <v>0.4509166666666668</v>
+        <v>0.45091666666666669</v>
       </c>
       <c r="AN15" t="s">
         <v>245</v>
@@ -74310,7 +74310,7 @@
         <v>285</v>
       </c>
       <c r="AM21">
-        <v>0.44941666666666663</v>
+        <v>0.44941666666666674</v>
       </c>
       <c r="AN21" t="s">
         <v>245</v>
@@ -74348,7 +74348,7 @@
         <v>285</v>
       </c>
       <c r="AM22">
-        <v>0.4469583333333334</v>
+        <v>0.44695833333333335</v>
       </c>
       <c r="AN22" t="s">
         <v>245</v>
@@ -74424,7 +74424,7 @@
         <v>285</v>
       </c>
       <c r="AM24">
-        <v>0.44499166666666673</v>
+        <v>0.44499166666666667</v>
       </c>
       <c r="AN24" t="s">
         <v>245</v>
@@ -74462,7 +74462,7 @@
         <v>285</v>
       </c>
       <c r="AM25">
-        <v>0.45474166666666666</v>
+        <v>0.4547416666666666</v>
       </c>
       <c r="AN25" t="s">
         <v>245</v>
@@ -74500,7 +74500,7 @@
         <v>285</v>
       </c>
       <c r="AM26">
-        <v>0.45130833333333326</v>
+        <v>0.45130833333333337</v>
       </c>
       <c r="AN26" t="s">
         <v>245</v>
@@ -74576,7 +74576,7 @@
         <v>285</v>
       </c>
       <c r="AM28">
-        <v>0.44241666666666674</v>
+        <v>0.44241666666666668</v>
       </c>
       <c r="AN28" t="s">
         <v>245</v>
@@ -74614,7 +74614,7 @@
         <v>285</v>
       </c>
       <c r="AM29">
-        <v>0.44885000000000003</v>
+        <v>0.44884999999999997</v>
       </c>
       <c r="AN29" t="s">
         <v>245</v>
@@ -74690,7 +74690,7 @@
         <v>285</v>
       </c>
       <c r="AM31">
-        <v>0.43934166666666657</v>
+        <v>0.43934166666666669</v>
       </c>
       <c r="AN31" t="s">
         <v>245</v>
@@ -74728,7 +74728,7 @@
         <v>285</v>
       </c>
       <c r="AM32">
-        <v>0.44870833333333343</v>
+        <v>0.44870833333333332</v>
       </c>
       <c r="AN32" t="s">
         <v>245</v>
@@ -74766,7 +74766,7 @@
         <v>285</v>
       </c>
       <c r="AM33">
-        <v>0.45370833333333321</v>
+        <v>0.45370833333333332</v>
       </c>
       <c r="AN33" t="s">
         <v>245</v>
@@ -74792,7 +74792,7 @@
         <v>285</v>
       </c>
       <c r="AM34">
-        <v>0.43429166666666674</v>
+        <v>0.43429166666666658</v>
       </c>
       <c r="AN34" t="s">
         <v>245</v>
@@ -74844,7 +74844,7 @@
         <v>285</v>
       </c>
       <c r="AM36">
-        <v>0.38044166666666662</v>
+        <v>0.38044166666666673</v>
       </c>
       <c r="AN36" t="s">
         <v>245</v>
@@ -74870,7 +74870,7 @@
         <v>285</v>
       </c>
       <c r="AM37">
-        <v>0.37212499999999998</v>
+        <v>0.37212500000000004</v>
       </c>
       <c r="AN37" t="s">
         <v>245</v>
@@ -74910,7 +74910,7 @@
         <v>285</v>
       </c>
       <c r="AM39">
-        <v>0.37856666666666672</v>
+        <v>0.37856666666666666</v>
       </c>
       <c r="AN39" t="s">
         <v>245</v>
@@ -74922,7 +74922,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C20300F0-29DA-436E-98B9-33E58DAC32F2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C50BC9B-8048-44DE-8CCC-E21DD858C81C}">
   <dimension ref="A9:AN346"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -75412,7 +75412,7 @@
         <v>293</v>
       </c>
       <c r="AM14">
-        <v>0.59216122489040124</v>
+        <v>0.59216122489040113</v>
       </c>
       <c r="AN14" t="s">
         <v>245</v>
@@ -75492,7 +75492,7 @@
         <v>288</v>
       </c>
       <c r="AM15">
-        <v>0.45757967269595179</v>
+        <v>0.45757967269595173</v>
       </c>
       <c r="AN15" t="s">
         <v>245</v>
@@ -75892,7 +75892,7 @@
         <v>290</v>
       </c>
       <c r="AM20">
-        <v>0.3947167347392404</v>
+        <v>0.39471673473924035</v>
       </c>
       <c r="AN20" t="s">
         <v>245</v>
@@ -76642,7 +76642,7 @@
         <v>290</v>
       </c>
       <c r="AM32">
-        <v>0.47813333333333335</v>
+        <v>0.4781333333333333</v>
       </c>
       <c r="AN32" t="s">
         <v>245</v>
@@ -77760,7 +77760,7 @@
         <v>293</v>
       </c>
       <c r="AM54">
-        <v>0.46213333333333328</v>
+        <v>0.46213333333333334</v>
       </c>
       <c r="AN54" t="s">
         <v>245</v>
@@ -77810,7 +77810,7 @@
         <v>288</v>
       </c>
       <c r="AM55">
-        <v>0.47316666666666668</v>
+        <v>0.47316666666666674</v>
       </c>
       <c r="AN55" t="s">
         <v>245</v>
@@ -78010,7 +78010,7 @@
         <v>288</v>
       </c>
       <c r="AM59">
-        <v>0.42896666666666666</v>
+        <v>0.42896666666666672</v>
       </c>
       <c r="AN59" t="s">
         <v>245</v>
@@ -78060,7 +78060,7 @@
         <v>290</v>
       </c>
       <c r="AM60">
-        <v>0.40983333333333327</v>
+        <v>0.40983333333333333</v>
       </c>
       <c r="AN60" t="s">
         <v>245</v>
@@ -78660,7 +78660,7 @@
         <v>290</v>
       </c>
       <c r="AM72">
-        <v>0.43156666666666665</v>
+        <v>0.43156666666666671</v>
       </c>
       <c r="AN72" t="s">
         <v>245</v>
@@ -78960,7 +78960,7 @@
         <v>293</v>
       </c>
       <c r="AM78">
-        <v>0.43856666666666672</v>
+        <v>0.4385666666666666</v>
       </c>
       <c r="AN78" t="s">
         <v>245</v>
@@ -79160,7 +79160,7 @@
         <v>293</v>
       </c>
       <c r="AM82">
-        <v>0.45873333333333327</v>
+        <v>0.45873333333333338</v>
       </c>
       <c r="AN82" t="s">
         <v>245</v>
@@ -79560,7 +79560,7 @@
         <v>293</v>
       </c>
       <c r="AM90">
-        <v>0.45589999999999997</v>
+        <v>0.45590000000000003</v>
       </c>
       <c r="AN90" t="s">
         <v>245</v>
@@ -80260,7 +80260,7 @@
         <v>290</v>
       </c>
       <c r="AM104">
-        <v>0.42700000000000005</v>
+        <v>0.42699999999999999</v>
       </c>
       <c r="AN104" t="s">
         <v>245</v>
@@ -80360,7 +80360,7 @@
         <v>293</v>
       </c>
       <c r="AM106">
-        <v>0.43860000000000005</v>
+        <v>0.43859999999999993</v>
       </c>
       <c r="AN106" t="s">
         <v>245</v>
@@ -80410,7 +80410,7 @@
         <v>288</v>
       </c>
       <c r="AM107">
-        <v>0.39363333333333334</v>
+        <v>0.39363333333333328</v>
       </c>
       <c r="AN107" t="s">
         <v>245</v>
@@ -80960,7 +80960,7 @@
         <v>293</v>
       </c>
       <c r="AM118">
-        <v>0.4030333333333333</v>
+        <v>0.40303333333333335</v>
       </c>
       <c r="AN118" t="s">
         <v>245</v>
@@ -81010,7 +81010,7 @@
         <v>288</v>
       </c>
       <c r="AM119">
-        <v>0.34783333333333327</v>
+        <v>0.34783333333333338</v>
       </c>
       <c r="AN119" t="s">
         <v>245</v>
@@ -81060,7 +81060,7 @@
         <v>290</v>
       </c>
       <c r="AM120">
-        <v>0.34769999999999995</v>
+        <v>0.34770000000000006</v>
       </c>
       <c r="AN120" t="s">
         <v>245</v>

--- a/VerveStacks_KEN_grids_kan/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_KEN_grids_kan/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_KEN_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C9FBF56C-C9E6-4B06-B2B5-7839EF9F111B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B50BADEC-FCBD-44CB-BAE5-D1CB05E1AFD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -799,13 +799,13 @@
     <t>D</t>
   </si>
   <si>
-    <t>S02aH01,S03aH01,S01aH01,S04aH01</t>
+    <t>S03aH01,S02aH01,S01aH01,S04aH01</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S04aH03,S02aH02,S01aH03,S01aH02,S02aH03,S04aH02,S03aH03,S03aH02</t>
+    <t>S03aH03,S02aH02,S04aH03,S03aH02,S04aH02,S02aH03,S01aH02,S01aH03</t>
   </si>
   <si>
     <t>com_pkflx</t>
@@ -931,10 +931,10 @@
     <t>S07aH06</t>
   </si>
   <si>
-    <t>S06aH04,S02aH04,S01aH03,S05aH02,S05aH03,S03aH02,S03aH04,S02aH03,S07aH03,S01aH02,S04aH04,S02aH02,S01aH04,S07aH02,S04aH03,S07aH04,S04aH02,S05aH04,S06aH02,S06aH03,S03aH03</t>
+    <t>S05aH04,S06aH02,S06aH03,S02aH03,S07aH03,S01aH03,S05aH02,S05aH03,S03aH02,S03aH03,S04aH02,S03aH04,S01aH04,S07aH02,S02aH04,S02aH02,S06aH04,S04aH03,S07aH04,S01aH02,S04aH04</t>
   </si>
   <si>
-    <t>S02aH05,S02aH06,S03aH05,S05aH05,S04aH05,S06aH01,S05aH01,S07aH06,S01aH01,S04aH01,S04aH06,S01aH05,S03aH06,S06aH05,S03aH01,S02aH01,S05aH06,S07aH05,S01aH06,S07aH01,S06aH06</t>
+    <t>S01aH06,S07aH01,S01aH01,S04aH01,S04aH06,S04aH05,S06aH01,S06aH06,S07aH05,S05aH01,S07aH06,S02aH06,S03aH05,S05aH05,S03aH01,S02aH05,S02aH01,S05aH06,S01aH05,S03aH06,S06aH05</t>
   </si>
   <si>
     <t>AllS</t>
@@ -1000,10 +1000,10 @@
     <t>WaP</t>
   </si>
   <si>
-    <t>FaD,RaP,SaD,FaP,SaP,WaD,RaD,WaP</t>
+    <t>SaD,RaD,FaD,FaP,SaP,WaP,WaD,RaP</t>
   </si>
   <si>
-    <t>RaP,WaP,FaP,SaP,SaN,WaN,FaN,RaN</t>
+    <t>FaP,SaP,WaP,RaP,RaN,FaN,SaN,WaN</t>
   </si>
 </sst>
 </file>
@@ -24707,7 +24707,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA1A6B3F-42DD-4477-8E1B-63F19CB41BDC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DFC83F2-1ADF-4BF6-B8FB-6656FF1AF392}">
   <dimension ref="A9:AN346"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -25114,7 +25114,7 @@
         <v>158</v>
       </c>
       <c r="AM13">
-        <v>0.5496069395500135</v>
+        <v>0.54960693955001361</v>
       </c>
       <c r="AN13" t="s">
         <v>245</v>
@@ -26014,7 +26014,7 @@
         <v>158</v>
       </c>
       <c r="AM25">
-        <v>0.3714142857142857</v>
+        <v>0.37141428571428575</v>
       </c>
       <c r="AN25" t="s">
         <v>245</v>
@@ -27895,7 +27895,7 @@
         <v>158</v>
       </c>
       <c r="AM61">
-        <v>0.43405714285714281</v>
+        <v>0.43405714285714286</v>
       </c>
       <c r="AN61" t="s">
         <v>245</v>
@@ -28295,7 +28295,7 @@
         <v>158</v>
       </c>
       <c r="AM69">
-        <v>0.4516857142857143</v>
+        <v>0.45168571428571436</v>
       </c>
       <c r="AN69" t="s">
         <v>245</v>
@@ -28495,7 +28495,7 @@
         <v>158</v>
       </c>
       <c r="AM73">
-        <v>0.45615714285714287</v>
+        <v>0.45615714285714282</v>
       </c>
       <c r="AN73" t="s">
         <v>245</v>
@@ -29495,7 +29495,7 @@
         <v>158</v>
       </c>
       <c r="AM93">
-        <v>0.42887142857142863</v>
+        <v>0.42887142857142857</v>
       </c>
       <c r="AN93" t="s">
         <v>245</v>
@@ -29695,7 +29695,7 @@
         <v>158</v>
       </c>
       <c r="AM97">
-        <v>0.4422428571428571</v>
+        <v>0.44224285714285722</v>
       </c>
       <c r="AN97" t="s">
         <v>245</v>
@@ -30095,7 +30095,7 @@
         <v>158</v>
       </c>
       <c r="AM105">
-        <v>0.42919999999999991</v>
+        <v>0.42920000000000008</v>
       </c>
       <c r="AN105" t="s">
         <v>245</v>
@@ -31095,7 +31095,7 @@
         <v>158</v>
       </c>
       <c r="AM125">
-        <v>0.3771714285714286</v>
+        <v>0.37717142857142855</v>
       </c>
       <c r="AN125" t="s">
         <v>245</v>
@@ -36205,7 +36205,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{880C3CAD-F8C4-4449-803F-96D991B523B2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A1AFE38-76AC-48F3-982C-7D8D9A0CE4F4}">
   <dimension ref="A9:AN1186"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -39522,7 +39522,7 @@
         <v>160</v>
       </c>
       <c r="AM49">
-        <v>0.49716000000000005</v>
+        <v>0.49715999999999994</v>
       </c>
       <c r="AN49" t="s">
         <v>245</v>
@@ -39998,7 +39998,7 @@
         <v>160</v>
       </c>
       <c r="AM56">
-        <v>0.52045999999999992</v>
+        <v>0.52046000000000003</v>
       </c>
       <c r="AN56" t="s">
         <v>245</v>
@@ -44540,7 +44540,7 @@
         <v>160</v>
       </c>
       <c r="AM140">
-        <v>0.43318000000000001</v>
+        <v>0.43317999999999995</v>
       </c>
       <c r="AN140" t="s">
         <v>245</v>
@@ -46640,7 +46640,7 @@
         <v>160</v>
       </c>
       <c r="AM182">
-        <v>0.38904</v>
+        <v>0.38903999999999994</v>
       </c>
       <c r="AN182" t="s">
         <v>245</v>
@@ -73584,7 +73584,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26DDBE97-F47F-48E6-970C-B4CDD6D69964}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4D0508C-07EC-426D-B0A2-C2442AB877FF}">
   <dimension ref="A9:AN39"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -73972,7 +73972,7 @@
         <v>285</v>
       </c>
       <c r="AM14">
-        <v>0.37885833333333335</v>
+        <v>0.3788583333333333</v>
       </c>
       <c r="AN14" t="s">
         <v>245</v>
@@ -74022,7 +74022,7 @@
         <v>285</v>
       </c>
       <c r="AM15">
-        <v>0.45091666666666669</v>
+        <v>0.45091666666666663</v>
       </c>
       <c r="AN15" t="s">
         <v>245</v>
@@ -74222,7 +74222,7 @@
         <v>285</v>
       </c>
       <c r="AM19">
-        <v>0.52139999999999997</v>
+        <v>0.52140000000000009</v>
       </c>
       <c r="AN19" t="s">
         <v>245</v>
@@ -74310,7 +74310,7 @@
         <v>285</v>
       </c>
       <c r="AM21">
-        <v>0.44941666666666674</v>
+        <v>0.44941666666666663</v>
       </c>
       <c r="AN21" t="s">
         <v>245</v>
@@ -74462,7 +74462,7 @@
         <v>285</v>
       </c>
       <c r="AM25">
-        <v>0.4547416666666666</v>
+        <v>0.45474166666666666</v>
       </c>
       <c r="AN25" t="s">
         <v>245</v>
@@ -74576,7 +74576,7 @@
         <v>285</v>
       </c>
       <c r="AM28">
-        <v>0.44241666666666668</v>
+        <v>0.44241666666666674</v>
       </c>
       <c r="AN28" t="s">
         <v>245</v>
@@ -74614,7 +74614,7 @@
         <v>285</v>
       </c>
       <c r="AM29">
-        <v>0.44884999999999997</v>
+        <v>0.44885000000000003</v>
       </c>
       <c r="AN29" t="s">
         <v>245</v>
@@ -74652,7 +74652,7 @@
         <v>285</v>
       </c>
       <c r="AM30">
-        <v>0.44701666666666662</v>
+        <v>0.44701666666666667</v>
       </c>
       <c r="AN30" t="s">
         <v>245</v>
@@ -74792,7 +74792,7 @@
         <v>285</v>
       </c>
       <c r="AM34">
-        <v>0.43429166666666658</v>
+        <v>0.43429166666666669</v>
       </c>
       <c r="AN34" t="s">
         <v>245</v>
@@ -74870,7 +74870,7 @@
         <v>285</v>
       </c>
       <c r="AM37">
-        <v>0.37212500000000004</v>
+        <v>0.37212499999999998</v>
       </c>
       <c r="AN37" t="s">
         <v>245</v>
@@ -74922,7 +74922,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C50BC9B-8048-44DE-8CCC-E21DD858C81C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4682FC12-E28B-47F7-8D70-F2E3583CDB93}">
   <dimension ref="A9:AN346"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -76642,7 +76642,7 @@
         <v>290</v>
       </c>
       <c r="AM32">
-        <v>0.4781333333333333</v>
+        <v>0.47813333333333335</v>
       </c>
       <c r="AN32" t="s">
         <v>245</v>
@@ -77310,7 +77310,7 @@
         <v>291</v>
       </c>
       <c r="AM45">
-        <v>0.52269999999999994</v>
+        <v>0.52270000000000005</v>
       </c>
       <c r="AN45" t="s">
         <v>245</v>
@@ -77410,7 +77410,7 @@
         <v>288</v>
       </c>
       <c r="AM47">
-        <v>0.44223333333333331</v>
+        <v>0.44223333333333342</v>
       </c>
       <c r="AN47" t="s">
         <v>245</v>
@@ -78010,7 +78010,7 @@
         <v>288</v>
       </c>
       <c r="AM59">
-        <v>0.42896666666666672</v>
+        <v>0.42896666666666666</v>
       </c>
       <c r="AN59" t="s">
         <v>245</v>
@@ -78660,7 +78660,7 @@
         <v>290</v>
       </c>
       <c r="AM72">
-        <v>0.43156666666666671</v>
+        <v>0.43156666666666665</v>
       </c>
       <c r="AN72" t="s">
         <v>245</v>
@@ -79110,7 +79110,7 @@
         <v>291</v>
       </c>
       <c r="AM81">
-        <v>0.43593333333333328</v>
+        <v>0.43593333333333334</v>
       </c>
       <c r="AN81" t="s">
         <v>245</v>
@@ -79210,7 +79210,7 @@
         <v>288</v>
       </c>
       <c r="AM83">
-        <v>0.47026666666666667</v>
+        <v>0.47026666666666661</v>
       </c>
       <c r="AN83" t="s">
         <v>245</v>
@@ -79310,7 +79310,7 @@
         <v>291</v>
       </c>
       <c r="AM85">
-        <v>0.43660000000000004</v>
+        <v>0.43659999999999993</v>
       </c>
       <c r="AN85" t="s">
         <v>245</v>
@@ -79660,7 +79660,7 @@
         <v>290</v>
       </c>
       <c r="AM92">
-        <v>0.40710000000000002</v>
+        <v>0.40709999999999996</v>
       </c>
       <c r="AN92" t="s">
         <v>245</v>
@@ -79710,7 +79710,7 @@
         <v>291</v>
       </c>
       <c r="AM93">
-        <v>0.45920000000000005</v>
+        <v>0.4592</v>
       </c>
       <c r="AN93" t="s">
         <v>245</v>
@@ -79810,7 +79810,7 @@
         <v>288</v>
       </c>
       <c r="AM95">
-        <v>0.44166666666666665</v>
+        <v>0.44166666666666671</v>
       </c>
       <c r="AN95" t="s">
         <v>245</v>
@@ -80010,7 +80010,7 @@
         <v>288</v>
       </c>
       <c r="AM99">
-        <v>0.47016666666666662</v>
+        <v>0.47016666666666668</v>
       </c>
       <c r="AN99" t="s">
         <v>245</v>
@@ -80410,7 +80410,7 @@
         <v>288</v>
       </c>
       <c r="AM107">
-        <v>0.39363333333333328</v>
+        <v>0.39363333333333334</v>
       </c>
       <c r="AN107" t="s">
         <v>245</v>
@@ -81060,7 +81060,7 @@
         <v>290</v>
       </c>
       <c r="AM120">
-        <v>0.34770000000000006</v>
+        <v>0.34769999999999995</v>
       </c>
       <c r="AN120" t="s">
         <v>245</v>

--- a/VerveStacks_KEN_grids_kan/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_KEN_grids_kan/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_KEN_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B50BADEC-FCBD-44CB-BAE5-D1CB05E1AFD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7C547BC1-EBE8-4534-9953-C472DCCCDC3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -799,13 +799,13 @@
     <t>D</t>
   </si>
   <si>
-    <t>S03aH01,S02aH01,S01aH01,S04aH01</t>
+    <t>S02aH01,S03aH01,S01aH01,S04aH01</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S03aH03,S02aH02,S04aH03,S03aH02,S04aH02,S02aH03,S01aH02,S01aH03</t>
+    <t>S01aH02,S04aH02,S03aH02,S04aH03,S03aH03,S02aH02,S02aH03,S01aH03</t>
   </si>
   <si>
     <t>com_pkflx</t>
@@ -931,10 +931,10 @@
     <t>S07aH06</t>
   </si>
   <si>
-    <t>S05aH04,S06aH02,S06aH03,S02aH03,S07aH03,S01aH03,S05aH02,S05aH03,S03aH02,S03aH03,S04aH02,S03aH04,S01aH04,S07aH02,S02aH04,S02aH02,S06aH04,S04aH03,S07aH04,S01aH02,S04aH04</t>
+    <t>S01aH04,S07aH02,S03aH02,S03aH04,S03aH03,S06aH04,S04aH03,S07aH04,S04aH02,S02aH03,S07aH03,S02aH02,S01aH02,S04aH04,S02aH04,S01aH03,S05aH02,S05aH03,S05aH04,S06aH02,S06aH03</t>
   </si>
   <si>
-    <t>S01aH06,S07aH01,S01aH01,S04aH01,S04aH06,S04aH05,S06aH01,S06aH06,S07aH05,S05aH01,S07aH06,S02aH06,S03aH05,S05aH05,S03aH01,S02aH05,S02aH01,S05aH06,S01aH05,S03aH06,S06aH05</t>
+    <t>S05aH01,S07aH06,S06aH06,S02aH05,S02aH01,S05aH06,S07aH05,S01aH01,S04aH01,S04aH06,S04aH05,S06aH01,S03aH01,S01aH05,S03aH06,S06aH05,S02aH06,S03aH05,S05aH05,S01aH06,S07aH01</t>
   </si>
   <si>
     <t>AllS</t>
@@ -1000,10 +1000,10 @@
     <t>WaP</t>
   </si>
   <si>
-    <t>SaD,RaD,FaD,FaP,SaP,WaP,WaD,RaP</t>
+    <t>FaD,WaP,RaD,RaP,FaP,SaP,SaD,WaD</t>
   </si>
   <si>
-    <t>FaP,SaP,WaP,RaP,RaN,FaN,SaN,WaN</t>
+    <t>RaP,RaN,WaP,FaN,FaP,SaP,SaN,WaN</t>
   </si>
 </sst>
 </file>
@@ -24707,7 +24707,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DFC83F2-1ADF-4BF6-B8FB-6656FF1AF392}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5FB66B28-01F1-425A-A72B-D955EDCF585B}">
   <dimension ref="A9:AN346"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -25114,7 +25114,7 @@
         <v>158</v>
       </c>
       <c r="AM13">
-        <v>0.54960693955001361</v>
+        <v>0.5496069395500135</v>
       </c>
       <c r="AN13" t="s">
         <v>245</v>
@@ -25437,7 +25437,7 @@
         <v>158</v>
       </c>
       <c r="AM17">
-        <v>0.48218899963086009</v>
+        <v>0.48218899963086015</v>
       </c>
       <c r="AN17" t="s">
         <v>245</v>
@@ -26014,7 +26014,7 @@
         <v>158</v>
       </c>
       <c r="AM25">
-        <v>0.37141428571428575</v>
+        <v>0.3714142857142857</v>
       </c>
       <c r="AN25" t="s">
         <v>245</v>
@@ -26250,7 +26250,7 @@
         <v>158</v>
       </c>
       <c r="AM29">
-        <v>0.44557142857142862</v>
+        <v>0.44557142857142856</v>
       </c>
       <c r="AN29" t="s">
         <v>245</v>
@@ -28495,7 +28495,7 @@
         <v>158</v>
       </c>
       <c r="AM73">
-        <v>0.45615714285714282</v>
+        <v>0.45615714285714287</v>
       </c>
       <c r="AN73" t="s">
         <v>245</v>
@@ -29095,7 +29095,7 @@
         <v>158</v>
       </c>
       <c r="AM85">
-        <v>0.43557142857142855</v>
+        <v>0.4355714285714285</v>
       </c>
       <c r="AN85" t="s">
         <v>245</v>
@@ -29495,7 +29495,7 @@
         <v>158</v>
       </c>
       <c r="AM93">
-        <v>0.42887142857142857</v>
+        <v>0.42887142857142863</v>
       </c>
       <c r="AN93" t="s">
         <v>245</v>
@@ -29695,7 +29695,7 @@
         <v>158</v>
       </c>
       <c r="AM97">
-        <v>0.44224285714285722</v>
+        <v>0.4422428571428571</v>
       </c>
       <c r="AN97" t="s">
         <v>245</v>
@@ -30095,7 +30095,7 @@
         <v>158</v>
       </c>
       <c r="AM105">
-        <v>0.42920000000000008</v>
+        <v>0.42919999999999997</v>
       </c>
       <c r="AN105" t="s">
         <v>245</v>
@@ -31095,7 +31095,7 @@
         <v>158</v>
       </c>
       <c r="AM125">
-        <v>0.37717142857142855</v>
+        <v>0.3771714285714286</v>
       </c>
       <c r="AN125" t="s">
         <v>245</v>
@@ -36205,7 +36205,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A1AFE38-76AC-48F3-982C-7D8D9A0CE4F4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84DF8687-14DD-4243-9386-9B608E33701A}">
   <dimension ref="A9:AN1186"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -37842,7 +37842,7 @@
         <v>160</v>
       </c>
       <c r="AM28">
-        <v>0.40520546803367508</v>
+        <v>0.40520546803367513</v>
       </c>
       <c r="AN28" t="s">
         <v>245</v>
@@ -38402,7 +38402,7 @@
         <v>160</v>
       </c>
       <c r="AM35">
-        <v>0.36392000000000002</v>
+        <v>0.36391999999999997</v>
       </c>
       <c r="AN35" t="s">
         <v>245</v>
@@ -39998,7 +39998,7 @@
         <v>160</v>
       </c>
       <c r="AM56">
-        <v>0.52046000000000003</v>
+        <v>0.52045999999999992</v>
       </c>
       <c r="AN56" t="s">
         <v>245</v>
@@ -41650,7 +41650,7 @@
         <v>160</v>
       </c>
       <c r="AM84">
-        <v>0.44189999999999996</v>
+        <v>0.44190000000000007</v>
       </c>
       <c r="AN84" t="s">
         <v>245</v>
@@ -44890,7 +44890,7 @@
         <v>160</v>
       </c>
       <c r="AM147">
-        <v>0.45234000000000008</v>
+        <v>0.45233999999999996</v>
       </c>
       <c r="AN147" t="s">
         <v>245</v>
@@ -45240,7 +45240,7 @@
         <v>160</v>
       </c>
       <c r="AM154">
-        <v>0.43945999999999996</v>
+        <v>0.43946000000000007</v>
       </c>
       <c r="AN154" t="s">
         <v>245</v>
@@ -45940,7 +45940,7 @@
         <v>160</v>
       </c>
       <c r="AM168">
-        <v>0.44874000000000003</v>
+        <v>0.44873999999999992</v>
       </c>
       <c r="AN168" t="s">
         <v>245</v>
@@ -48040,7 +48040,7 @@
         <v>160</v>
       </c>
       <c r="AM210">
-        <v>0.38140000000000002</v>
+        <v>0.38139999999999996</v>
       </c>
       <c r="AN210" t="s">
         <v>245</v>
@@ -73584,7 +73584,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4D0508C-07EC-426D-B0A2-C2442AB877FF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA8BC89E-3C69-4FF5-867A-54E32321B515}">
   <dimension ref="A9:AN39"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -73922,7 +73922,7 @@
         <v>285</v>
       </c>
       <c r="AM13">
-        <v>0.40084425868371848</v>
+        <v>0.40084425868371859</v>
       </c>
       <c r="AN13" t="s">
         <v>245</v>
@@ -73972,7 +73972,7 @@
         <v>285</v>
       </c>
       <c r="AM14">
-        <v>0.3788583333333333</v>
+        <v>0.37885833333333335</v>
       </c>
       <c r="AN14" t="s">
         <v>245</v>
@@ -74222,7 +74222,7 @@
         <v>285</v>
       </c>
       <c r="AM19">
-        <v>0.52140000000000009</v>
+        <v>0.52139999999999997</v>
       </c>
       <c r="AN19" t="s">
         <v>245</v>
@@ -74348,7 +74348,7 @@
         <v>285</v>
       </c>
       <c r="AM22">
-        <v>0.44695833333333335</v>
+        <v>0.4469583333333334</v>
       </c>
       <c r="AN22" t="s">
         <v>245</v>
@@ -74576,7 +74576,7 @@
         <v>285</v>
       </c>
       <c r="AM28">
-        <v>0.44241666666666674</v>
+        <v>0.44241666666666668</v>
       </c>
       <c r="AN28" t="s">
         <v>245</v>
@@ -74614,7 +74614,7 @@
         <v>285</v>
       </c>
       <c r="AM29">
-        <v>0.44885000000000003</v>
+        <v>0.44885000000000014</v>
       </c>
       <c r="AN29" t="s">
         <v>245</v>
@@ -74690,7 +74690,7 @@
         <v>285</v>
       </c>
       <c r="AM31">
-        <v>0.43934166666666669</v>
+        <v>0.43934166666666657</v>
       </c>
       <c r="AN31" t="s">
         <v>245</v>
@@ -74728,7 +74728,7 @@
         <v>285</v>
       </c>
       <c r="AM32">
-        <v>0.44870833333333332</v>
+        <v>0.44870833333333326</v>
       </c>
       <c r="AN32" t="s">
         <v>245</v>
@@ -74766,7 +74766,7 @@
         <v>285</v>
       </c>
       <c r="AM33">
-        <v>0.45370833333333332</v>
+        <v>0.45370833333333338</v>
       </c>
       <c r="AN33" t="s">
         <v>245</v>
@@ -74792,7 +74792,7 @@
         <v>285</v>
       </c>
       <c r="AM34">
-        <v>0.43429166666666669</v>
+        <v>0.43429166666666674</v>
       </c>
       <c r="AN34" t="s">
         <v>245</v>
@@ -74844,7 +74844,7 @@
         <v>285</v>
       </c>
       <c r="AM36">
-        <v>0.38044166666666673</v>
+        <v>0.38044166666666662</v>
       </c>
       <c r="AN36" t="s">
         <v>245</v>
@@ -74910,7 +74910,7 @@
         <v>285</v>
       </c>
       <c r="AM39">
-        <v>0.37856666666666666</v>
+        <v>0.37856666666666672</v>
       </c>
       <c r="AN39" t="s">
         <v>245</v>
@@ -74922,7 +74922,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4682FC12-E28B-47F7-8D70-F2E3583CDB93}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3611E268-3971-4D79-B727-089463FAEB23}">
   <dimension ref="A9:AN346"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -77310,7 +77310,7 @@
         <v>291</v>
       </c>
       <c r="AM45">
-        <v>0.52270000000000005</v>
+        <v>0.52269999999999994</v>
       </c>
       <c r="AN45" t="s">
         <v>245</v>
@@ -79110,7 +79110,7 @@
         <v>291</v>
       </c>
       <c r="AM81">
-        <v>0.43593333333333334</v>
+        <v>0.43593333333333328</v>
       </c>
       <c r="AN81" t="s">
         <v>245</v>
@@ -79310,7 +79310,7 @@
         <v>291</v>
       </c>
       <c r="AM85">
-        <v>0.43659999999999993</v>
+        <v>0.43660000000000004</v>
       </c>
       <c r="AN85" t="s">
         <v>245</v>
@@ -79710,7 +79710,7 @@
         <v>291</v>
       </c>
       <c r="AM93">
-        <v>0.4592</v>
+        <v>0.45920000000000005</v>
       </c>
       <c r="AN93" t="s">
         <v>245</v>

--- a/VerveStacks_KEN_grids_kan/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_KEN_grids_kan/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_KEN_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D235F6A0-3E6D-40BD-B109-B4B38EBC1108}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DFA43EA-8E01-4033-B904-E8B13CF971FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6067,7 +6067,7 @@
         <v>82</v>
       </c>
       <c r="O4" s="10" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:39" x14ac:dyDescent="0.45">
